--- a/questionnaire_templates/042_development_knowledge_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/042_development_knowledge_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>development_knowledge_assessment</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Development Knowledge Assessment</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is a questionnaire to assess your development knowledge and experience.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>development_background</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Your Development Background</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your development background.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>programming_languages</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Programming Languages</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select all programming languages you are familiar with.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>development_environment</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Development Environment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select all development environments you are familiar with.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>development_process</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Development Process</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select all development processes you are familiar with.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>code_review</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Code Review</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please indicate how often you perform code review.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>testing_approach</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Testing Approach</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select all testing approaches you are familiar with.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>code_quality</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Code Quality</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please rate your code quality based on industry standards.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Time Management</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please indicate how you manage your time in development projects.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>continuous_integration</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Continuous Integration</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select all continuous integration tools you are familiar with.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>code_review_process</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Code Review Process</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please indicate how you perform code review.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>deployment_strategy</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Deployment Strategy</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select all deployment strategies you are familiar with.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>collaboration_tools</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Collaboration Tools</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select all collaboration tools you are familiar with.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>code_quality_check</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Code Quality Check</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please indicate how you perform code quality check.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>team_experience</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Team Experience</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please rate your team experience based on industry standards.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>code_mechanics</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Code Mechanics</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please rate your code mechanics based on industry standards.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>question_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question 17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please indicate how you manage your time in development projects.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_17</t>
+          <t>question_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>code_quality_check_process</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Collaboration Process</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please indicate your collaboration process.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -929,20 +1001,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question_18</t>
+          <t>question_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>collaboration_process</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Team Dynamics</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please rate your team dynamics based on industry standards.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -952,20 +1028,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question_19</t>
+          <t>question_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>team_dynamics</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Communication Skills</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please rate your communication skills based on industry standards.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -980,15 +1060,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>question_20</t>
+          <t>question_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>communication_skills</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Question 21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Please indicate how you perform code review.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
@@ -1003,15 +1087,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>question_21</t>
+          <t>question_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>code_review_process</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Testing Process</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Please indicate your testing process.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
@@ -1026,15 +1114,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>question_22</t>
+          <t>question_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>testing_process</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Please indicate how you receive feedback on your work.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
@@ -1049,62 +1141,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question_23</t>
+          <t>question_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>testing_process</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Question 24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Please indicate how you manage your time in development projects.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_26</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>time_management_process</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1149,24 +1199,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1183,7 +1233,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1205,12 +1255,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>visual_studio_code</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Visual Studio Code</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1272,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>intellij_idea</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IntelliJ IDEA</t>
+          <t>Ruby</t>
         </is>
       </c>
     </row>
@@ -1239,1168 +1289,1610 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eclipse</t>
+          <t>php</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eclipse</t>
+          <t>PHP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>waterfall</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>kotlin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Kotlin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>go</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Go</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>r</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>unit_testing</t>
+          <t>lua</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Lua</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>integration_testing</t>
+          <t>scala</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integration Testing</t>
+          <t>Scala</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>system_testing</t>
+          <t>rust</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>System Testing</t>
+          <t>Rust</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>haskell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Haskell</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>visual_studio_code</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Visual Studio Code</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>intellij_idea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>IntelliJ IDEA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>eclipse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Eclipse</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>visual_studio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Visual Studio</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kanban</t>
+          <t>netbeans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kanban</t>
+          <t>NetBeans</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jenkins</t>
+          <t>android_studio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Android Studio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>travis_ci</t>
+          <t>xcode</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Travis CI</t>
+          <t>Xcode</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>circleci</t>
+          <t>webstorm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CircleCI</t>
+          <t>WebStorm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>pycharm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>PyCharm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>visual_paradigm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Visual Paradigm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>rider</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Rider</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>devops</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>continuous_deployment</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Continuous Deployment</t>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>manual_deployment</t>
+          <t>scrum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Manual Deployment</t>
+          <t>Scrum</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jira</t>
+          <t>kanban</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jira</t>
+          <t>Kanban</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>asana</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>basecamp</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Basecamp</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>unit_testing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Unit Testing</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>integration_testing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Strongly Agree</t>
+          <t>Integration Testing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>system_testing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Somewhat Agree</t>
+          <t>System Testing</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>automated_testing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Somewhat Disagree</t>
+          <t>Automated Testing</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>manual_testing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Manual Testing</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kanban</t>
+          <t>scrum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kanban</t>
+          <t>Scrum</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>kanban</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Kanban</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>gantt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Gantt</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>jenkins</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Jenkins</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>travis_ci</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Travis CI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>circleci</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>CircleCI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>gitlab_ci</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>GitLab CI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>azure_pipelines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Azure Pipelines</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>appveyor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>AppVeyor</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>code_review</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Code Review</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>devops</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>DevOps</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>continuous_deployment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Continuous Deployment</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>manual_deployment</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Manual Deployment</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>jira</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Jira</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>unit_testing</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Asana</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>integration_testing</t>
+          <t>basecamp</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Integration Testing</t>
+          <t>Basecamp</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>system_testing</t>
+          <t>trello</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>System Testing</t>
+          <t>Trello</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>question_23_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>unit_testing</t>
+          <t>slack</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Slack</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>question_23_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>integration_testing</t>
+          <t>code_review</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Integration Testing</t>
+          <t>Code Review</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>question_23_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>system_testing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>System Testing</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>question_25_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>question_25_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>question_25_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>question_25_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>question_25_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>code_review</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Code Review</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>question_26_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>question_26_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>question_26_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>scrum</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>question_17_choices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>kanban</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Kanban</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>question_17_choices</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>gantt</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Gantt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>question_17_choices</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>waterfall</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Waterfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>question_18_choices</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>code_review</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Code Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>question_18_choices</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>question_19_choices</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>question_19_choices</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>question_19_choices</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>question_20_choices</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>question_20_choices</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>question_20_choices</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>question_21_choices</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>code_review</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Code Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>question_21_choices</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>question_22_choices</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>unit_testing</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Unit Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>question_22_choices</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>integration_testing</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Integration Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>question_22_choices</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>system_testing</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>System Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>question_22_choices</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>automated_testing</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Automated Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>question_22_choices</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>manual_testing</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Manual Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>question_23_choices</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>feedback</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>question_23_choices</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>code_review</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Code Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>question_23_choices</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>peer_review</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Peer Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>question_24_choices</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>agile</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Agile</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>question_24_choices</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>scrum</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>question_24_choices</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>kanban</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kanban</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>question_24_choices</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>gantt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Gantt</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>question_24_choices</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>waterfall</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
